--- a/docs/Logic Requirements/Ageipelago Joan of Arc.xlsx
+++ b/docs/Logic Requirements/Ageipelago Joan of Arc.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/BB6DD295C338E39F/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{BA2542DF-DBA3-4D13-8D9D-81B85B6B4E30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38727B9F-1E22-4033-AAF8-5C72A93D96F7}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B2EA931-9906-47E9-82BD-7BDE5EAB488E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9E5C4DF5-6A70-45B6-8795-4F3A15A3E9BB}"/>
   </bookViews>
@@ -37,33 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
-  <si>
-    <r>
-      <t xml:space="preserve">Once again, we might want to split Siege from non-Siege units for items.
-The additional Resources are given when destroying </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Burgundies Town Center</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, with the wood dependeing on their leftover Resources in Vanilla.</t>
-    </r>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
   <si>
     <t>6 Villagers</t>
   </si>
@@ -74,62 +48,10 @@
 100 Wood</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve"> Destroy </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Burgundies northern Town Center</t>
-    </r>
-  </si>
-  <si>
     <t>Bring the Cart carrying the French Flag to the flagged Hill</t>
   </si>
   <si>
     <t>A Perfect Martyr</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">BIG Scenario.
-I suggest seperating the starting army's siege and regular units.
-Not sure if the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>King's Men</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> CAN be defeated, but it SHOULD be possible.
-Lots of Enemies here, so I figured we'd do well to split them up into multiple Objectives.</t>
-    </r>
-  </si>
-  <si>
-    <t>10 Men-at-Arms
-2 Throwing Axemen
-2 Knights
-2 Heavy Scorpions</t>
-  </si>
-  <si>
-    <t>6 Villagers
-4 Villagers</t>
   </si>
   <si>
     <t>Joan of Arc
@@ -148,154 +70,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Optain 10 Villagers
-Bring 10 Villagers to </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF06CFEA"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Compiègne</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Destroy </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>1/2/3 English Castle/s</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat all </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>English Units south of the River</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat all </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>English units North of the River</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>English</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Burgundy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>King's Men</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF06CFEA"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Compiègne</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">Optain at least 6 Villagers
 Meet </t>
     </r>
@@ -330,13 +104,6 @@
   </si>
   <si>
     <t>The Siege of Paris</t>
-  </si>
-  <si>
-    <t>Misc. Buildings</t>
-  </si>
-  <si>
-    <t>6 Villagers
-1 Town Center</t>
   </si>
   <si>
     <t>Joan of Arc
@@ -352,141 +119,10 @@
 150 Stone</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Defeat </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Rheims</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Chalons</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Troyes</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Defeat </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>English Guards</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Destroy </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>the Town Center of Rheims</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Destroy </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>the Town Center of Chalons</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Destroy </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>the Town Center of Troyes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Reach the French Town</t>
-    </r>
-  </si>
-  <si>
     <t>The Rising</t>
   </si>
   <si>
     <t>I recommend making the Villagers or Resources an item, as only these 2 are needed for Vicory.</t>
-  </si>
-  <si>
-    <t>2 Transport Ships, 2 Demolition Ships</t>
   </si>
   <si>
     <t>Joan of Arc
@@ -502,124 +138,6 @@
 150 Stone</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Destroy </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>4 English Castles</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>English</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Fastolf's Army</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Burgundy</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Destroy </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>1/2 English Castle/s</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Kill </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Sir John Fastolf</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Destroy </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>3 English Castles</t>
-    </r>
-  </si>
-  <si>
     <t>The Cleansing of the Loire</t>
   </si>
   <si>
@@ -630,359 +148,12 @@
 1 Scout Cavalry</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Destroy </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>2/3/4 English</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Castle/s</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Northern Englis</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">h
-Defeat </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Southern English</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Burgundy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Chinon</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF06CFEA"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Blois</t>
-    </r>
-  </si>
-  <si>
     <t>The Maid of Orleans</t>
-  </si>
-  <si>
-    <t>Due to how powerfull they are, I would recommend turning the 2 hero knights in the starting units into an item, as they can kill just about everything on the map when used properly.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>4 Men-at-Arms</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (first camp)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>4 Crossbowmen</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (first camp)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>4 Men-at-Arms, 6 Pikemen, 1 Capped Ram</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (second camp)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>6 Crossbowmen, 2 Scorpions</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (third camp)</t>
-    </r>
-  </si>
-  <si>
-    <t>2 Transport Ships</t>
   </si>
   <si>
     <t>Joan the Maid
 Sieur Bertrand
 Sieur de Metz</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Defeat </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Highwaymen</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Destroy the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Burgundian Castle</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Burgundian Ambush</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Burgundy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Army of France</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Chinon</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Enter the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Burgundian Village</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Bring Joan to </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Chinon</t>
-    </r>
   </si>
   <si>
     <t>An unlikely Messiah</t>
@@ -1741,232 +912,6 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> and destroy their Castles.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>6 Trade Carts (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF06CFEA"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Blois</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>)
-3 Villagers (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="0" tint="-0.499984740745262"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Orlèans</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>)
-1 Town Center (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="0" tint="-0.499984740745262"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Orlèans</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>12 Crossbowmen, 8 Knights (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF03CBF3"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Blois</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>)
-2 Transport Ships, 1 Dock
-Misc. Buildings (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="0" tint="-0.499984740745262"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Orlèans</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>)
-1000 Food, 1500 Wood, 1500 Gold, 500 Stone</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Defeating </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="0" tint="-0.499984740745262"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Orléans</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> would be pointless, seeing as they only own the Cathedral that must survive.
-The Resources are given when the Trade Carts reach </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="0" tint="-0.499984740745262"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Orlèans</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Bring Joan to </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF06CFEA"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Blois</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Bring 6 Trade Carts to </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="0" tint="-0.499984740745262"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Orlèans</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Bring Joan to </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="0" tint="-0.499984740745262"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Orléans</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Destroy </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">1 English </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Castle</t>
     </r>
   </si>
   <si>
@@ -3103,11 +2048,6 @@
     </r>
   </si>
   <si>
-    <t>La Hire, Constable Richemont, 16 Arbalesters, 8 Champions, 8 Hussars, 6 Paladins, 2 Trebuchets (1 on Hard) (French Army)
-Jean Bureau, 8 Hand Cannoneers, 6 Bombard Cannons (3 on Hard) (French Artillery)
-400 Food, 400 Wood, 50 Gold, 150 Stone</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Reach the French Army
 Reach the French Artillery
@@ -3333,6 +2273,1248 @@
       </rPr>
       <t xml:space="preserve"> and reaching the Hill with the Flag is possible when the Player can build a base.</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>4 Men-at-Arms,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>4 Crossbowmen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (first camp)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>4 Men-at-Arms, 6 Pikemen, 1 Capped Ram</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (second camp)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>6 Crossbowmen, 2 Scorpions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (third camp)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Destroy </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>1/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Castles</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Reach the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Western Units</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Reach the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Southern Units</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Reach the Transport Ships
+Defeat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Burgundy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Army of France</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Chinon
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Defeat</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Highwaymen</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bring Joan the Maid to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Chinon</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Destroy </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>2/3/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>4/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF03CBF3"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>English Castle/s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Northern English</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Southern English</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Burgundy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Chinon</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF06CFEA"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Blois</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Destroy </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Castles</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Destroy </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">1/2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Castle/s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Kill </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Sir John Fastolf</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Destroy </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Castles</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>English</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fastolf's Army</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Burgundy</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Destroy </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rheims'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Chalons'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Troyes' </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Town Center</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Reach the French Town</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Defeat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rheims</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Chalons</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Troyes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> English Guards</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bring Joan of Arc to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Orléans</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Destroy </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>English Castle</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Bring Joan of Arc to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF03CBF3"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Blois</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Bring 6 Trade Carts to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Orlèans</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>12 Crossbowmen, 8 Knights (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF03CBF3"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Blois</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>)
+2 Transport Ships, 1 Dock (Gaia)
+1000 Food, 1500 Wood, 1500 Gold, 500 Stone</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>6 Trade Carts (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF06CFEA"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Blois</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>)
+3 Villagers, 1 Town Center, Misc. Buildings (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Orlèans</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Defeating </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Orléans</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> would be pointless, seeing as they only own the Cathedral that must survive.
+In Vanilla the Resources are given when the Trade Carts reach </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Orlèans</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> Destroy </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Burgundys </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>northern Town Center</t>
+    </r>
+  </si>
+  <si>
+    <t>6 Villagers
+4 Villagers
+(Gaia)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">
+Bring 10 Villagers to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF06CFEA"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Compiègne</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Destroy </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>1/2/3/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF03CBF3"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Castle/s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Kill all </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">English </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Units</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>south of the River</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Kill all </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">English </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Units</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>North of the River</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>English</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Burgundy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>King's Men</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF06CFEA"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Compiègne</t>
+    </r>
+  </si>
+  <si>
+    <t>2 Transport Ships
+(Gaia)</t>
+  </si>
+  <si>
+    <t>2 Transport Ships, 2 Demolition Ships (Gaia)</t>
+  </si>
+  <si>
+    <t>6 Villagers, 1 Town Center, Misc. Buildings
+(Gaia)</t>
+  </si>
+  <si>
+    <r>
+      <t>10 Men-at-Arms, 2 Throwing Axemen, 2 Knights, 2 Heavy Scorpions
+(Gaia)
+1 Militia, 1 Scout (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>King's Men</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>La Hire, Constable Richemont, 16 Arbalesters, 8 Champions, 8 Hussars, 6 Paladins, 2 Trebuchets (1 on Hard)
+Jean Bureau, 8 Hand Cannoneers, 6 Bombard Cannons (3 on Hard)
+(Gaia)
+400 Food, 400 Wood, 50 Gold, 150 Stone
+Walls, Gates (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Burgundy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Once again, we might want to split Siege from non-Siege Units for Items.
+The additional Resources are given when destroying </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Burgundies Town Center</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, with the Wood dependeing on their leftover Resources in Vanilla.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">BIG Scenario.
+I suggest seperating the Starting Army's Siege and regular Units.
+Not sure if the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>King's Men</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> CAN be defeated, but it SHOULD be possible.
+Lots of Enemies here, so I figured we'd do well to split them up into multiple Objectives.</t>
+    </r>
+  </si>
+  <si>
+    <t>Due to how powerfull they are, I would recommend turning the 2 Hero Knights in the starting Units into an Item, as they can kill just about everything on the Map when used properly.</t>
   </si>
 </sst>
 </file>
@@ -3418,19 +3600,6 @@
     </font>
     <font>
       <sz val="18"/>
-      <color rgb="FF3A3A3A"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color rgb="FF3A3A3A"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="18"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -3501,6 +3670,17 @@
       <sz val="14"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -3603,7 +3783,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3617,12 +3797,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3632,13 +3806,22 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3983,307 +4166,299 @@
   <sheetData>
     <row r="2" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:17" ht="70.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="12" t="s">
-        <v>45</v>
+      <c r="B3" s="10" t="s">
+        <v>23</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="J3" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="K3" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="L3" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="M3" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="N3" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="O3" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P3" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q3" s="10" t="s">
-        <v>53</v>
+        <v>18</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="O3" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P3" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q3" s="8" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="4" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="6" t="s">
+    <row r="4" spans="2:17" ht="375.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5" t="s">
         <v>37</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="N4" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="5" spans="2:17" ht="375.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="6" t="s">
-        <v>29</v>
+      <c r="B5" s="11" t="s">
+        <v>13</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>68</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="O5" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7" t="s">
-        <v>64</v>
+        <v>73</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="2:17" ht="338.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="5" t="s">
-        <v>26</v>
+      <c r="B6" s="12" t="s">
+        <v>11</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2" t="s">
-        <v>21</v>
+        <v>78</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7" t="s">
-        <v>73</v>
+        <v>9</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="4" t="s">
-        <v>19</v>
+      <c r="B7" s="11" t="s">
+        <v>8</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>17</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>13</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="H7" s="2"/>
       <c r="I7" s="1"/>
-      <c r="J7" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="7" t="s">
-        <v>77</v>
+      <c r="J7" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="4" t="s">
-        <v>12</v>
+      <c r="B8" s="11" t="s">
+        <v>6</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>10</v>
+        <v>76</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>4</v>
+      <c r="B9" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>2</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="L9" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="7" t="s">
-        <v>88</v>
+        <v>82</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Logic Requirements/Ageipelago Joan of Arc.xlsx
+++ b/docs/Logic Requirements/Ageipelago Joan of Arc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03CA79BE-D7FE-4FB0-B3A7-6B86E0F84366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4661DF3-6457-49C5-8C06-54BDDDD8BB71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{9E5C4DF5-6A70-45B6-8795-4F3A15A3E9BB}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{9E5C4DF5-6A70-45B6-8795-4F3A15A3E9BB}"/>
   </bookViews>
   <sheets>
     <sheet name="Joan of Arc" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="188">
   <si>
     <t>6 Villagers</t>
   </si>
@@ -3803,12 +3803,54 @@
   <si>
     <t>Two-Handed Swordsman</t>
   </si>
+  <si>
+    <t>Restrictions</t>
+  </si>
+  <si>
+    <t>Buildings</t>
+  </si>
+  <si>
+    <t>Units</t>
+  </si>
+  <si>
+    <t>Technologies</t>
+  </si>
+  <si>
+    <t>Unrestricted</t>
+  </si>
+  <si>
+    <t>Unavailable</t>
+  </si>
+  <si>
+    <t>Castle Age</t>
+  </si>
+  <si>
+    <t>Feudal - Castle Age</t>
+  </si>
+  <si>
+    <t>Mill-Technologies automatically researced for Franks</t>
+  </si>
+  <si>
+    <t>Castle - Imperial Age</t>
+  </si>
+  <si>
+    <t>No Handcannoneers
+No Bombard Cannons
+No Cannon Galleons</t>
+  </si>
+  <si>
+    <t>Mill-Technologies automatically researced for Franks
+No Sappers</t>
+  </si>
+  <si>
+    <t>Imperial Age</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="32" x14ac:knownFonts="1">
+  <fonts count="33" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3891,12 +3933,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="24"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -4017,6 +4053,18 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -4032,7 +4080,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -4168,11 +4216,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4201,16 +4273,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4234,7 +4303,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4255,16 +4324,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4273,7 +4342,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4285,10 +4354,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4297,19 +4369,46 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4653,8 +4752,8 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="2:17" ht="70.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="10" t="s">
+    <row r="3" spans="2:17" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="55" t="s">
         <v>23</v>
       </c>
       <c r="C3" s="4" t="s">
@@ -4704,7 +4803,7 @@
       </c>
     </row>
     <row r="4" spans="2:17" ht="375.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>15</v>
       </c>
       <c r="C4" s="7" t="s">
@@ -4748,7 +4847,7 @@
       </c>
     </row>
     <row r="5" spans="2:17" ht="375.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="10" t="s">
         <v>13</v>
       </c>
       <c r="C5" s="3" t="s">
@@ -4790,7 +4889,7 @@
       </c>
     </row>
     <row r="6" spans="2:17" ht="375.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="3" t="s">
@@ -4830,7 +4929,7 @@
       </c>
     </row>
     <row r="7" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -4868,7 +4967,7 @@
       </c>
     </row>
     <row r="8" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="s">
@@ -4908,10 +5007,10 @@
       </c>
     </row>
     <row r="9" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="12" t="s">
         <v>2</v>
       </c>
       <c r="D9" s="2" t="s">
@@ -4957,15 +5056,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB235E58-4C38-4EB7-AA36-684DD097C8C8}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="46" t="s">
+        <v>175</v>
+      </c>
+      <c r="C2" s="47"/>
+      <c r="D2" s="48"/>
       <c r="G2" s="4" t="s">
         <v>84</v>
       </c>
@@ -4979,196 +5084,252 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G3" s="17" t="s">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="49" t="s">
+        <v>181</v>
+      </c>
+      <c r="C3" s="50"/>
+      <c r="D3" s="51"/>
+      <c r="G3" s="16" t="s">
         <v>86</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K3" s="43" t="s">
+      <c r="K3" s="42" t="s">
         <v>112</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>178</v>
+      </c>
       <c r="G4" s="2" t="s">
         <v>87</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K4" s="25" t="s">
+      <c r="K4" s="24" t="s">
         <v>113</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G5" s="18" t="s">
+    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="52" t="s">
+        <v>180</v>
+      </c>
+      <c r="C5" s="52" t="s">
+        <v>180</v>
+      </c>
+      <c r="D5" s="52" t="s">
+        <v>180</v>
+      </c>
+      <c r="G5" s="17" t="s">
         <v>88</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K5" s="44" t="s">
+      <c r="K5" s="43" t="s">
         <v>114</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G6" s="18" t="s">
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="15"/>
+      <c r="G6" s="17" t="s">
         <v>89</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K6" s="25" t="s">
+      <c r="K6" s="24" t="s">
         <v>115</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G7" s="18" t="s">
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="53"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="15"/>
+      <c r="G7" s="17" t="s">
         <v>90</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K7" s="25" t="s">
+      <c r="K7" s="24" t="s">
         <v>116</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G8" s="18" t="s">
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="15"/>
+      <c r="G8" s="17" t="s">
         <v>91</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K8" s="25" t="s">
+      <c r="K8" s="24" t="s">
         <v>117</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G9" s="41" t="s">
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="53"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="15"/>
+      <c r="G9" s="40" t="s">
         <v>92</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K9" s="25" t="s">
+      <c r="K9" s="24" t="s">
         <v>118</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G10" s="19" t="s">
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="53"/>
+      <c r="C10" s="53"/>
+      <c r="D10" s="15"/>
+      <c r="G10" s="18" t="s">
         <v>93</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K10" s="25" t="s">
+      <c r="K10" s="24" t="s">
         <v>119</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G11" s="19" t="s">
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="15"/>
+      <c r="G11" s="18" t="s">
         <v>94</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K11" s="25" t="s">
+      <c r="K11" s="24" t="s">
         <v>120</v>
       </c>
       <c r="L11" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G12" s="19" t="s">
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="53"/>
+      <c r="C12" s="53"/>
+      <c r="D12" s="15"/>
+      <c r="G12" s="18" t="s">
         <v>95</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K12" s="25" t="s">
+      <c r="K12" s="24" t="s">
         <v>121</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G13" s="19" t="s">
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="53"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="15"/>
+      <c r="G13" s="18" t="s">
         <v>98</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K13" s="25" t="s">
+      <c r="K13" s="24" t="s">
         <v>122</v>
       </c>
       <c r="L13" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="G14" s="18" t="s">
+    <row r="14" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="15"/>
+      <c r="G14" s="17" t="s">
         <v>96</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="K14" s="25" t="s">
+      <c r="K14" s="24" t="s">
         <v>123</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G15" s="19" t="s">
+    <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B15" s="53"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="15"/>
+      <c r="G15" s="18" t="s">
         <v>99</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="K15" s="25" t="s">
+      <c r="K15" s="24" t="s">
         <v>124</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G16" s="20" t="s">
+    <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B16" s="53"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="15"/>
+      <c r="G16" s="19" t="s">
         <v>101</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="K16" s="25" t="s">
+      <c r="K16" s="24" t="s">
         <v>125</v>
       </c>
       <c r="L16" s="3" t="s">
@@ -5176,13 +5337,13 @@
       </c>
     </row>
     <row r="17" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G17" s="20" t="s">
+      <c r="G17" s="19" t="s">
         <v>102</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="K17" s="26" t="s">
+      <c r="K17" s="25" t="s">
         <v>126</v>
       </c>
       <c r="L17" s="3" t="s">
@@ -5190,13 +5351,13 @@
       </c>
     </row>
     <row r="18" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G18" s="18" t="s">
+      <c r="G18" s="17" t="s">
         <v>103</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="K18" s="19" t="s">
+      <c r="K18" s="18" t="s">
         <v>127</v>
       </c>
       <c r="L18" s="3" t="s">
@@ -5204,13 +5365,13 @@
       </c>
     </row>
     <row r="19" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G19" s="21" t="s">
+      <c r="G19" s="20" t="s">
         <v>104</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="K19" s="19" t="s">
+      <c r="K19" s="18" t="s">
         <v>128</v>
       </c>
       <c r="L19" s="3" t="s">
@@ -5218,13 +5379,13 @@
       </c>
     </row>
     <row r="20" spans="7:12" ht="131.25" x14ac:dyDescent="0.25">
-      <c r="G20" s="18" t="s">
+      <c r="G20" s="17" t="s">
         <v>105</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="K20" s="19" t="s">
+      <c r="K20" s="18" t="s">
         <v>129</v>
       </c>
       <c r="L20" s="3" t="s">
@@ -5232,13 +5393,13 @@
       </c>
     </row>
     <row r="21" spans="7:12" ht="93.75" x14ac:dyDescent="0.25">
-      <c r="G21" s="22" t="s">
+      <c r="G21" s="21" t="s">
         <v>108</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="K21" s="19" t="s">
+      <c r="K21" s="18" t="s">
         <v>130</v>
       </c>
       <c r="L21" s="3" t="s">
@@ -5246,13 +5407,13 @@
       </c>
     </row>
     <row r="22" spans="7:12" ht="93.75" x14ac:dyDescent="0.25">
-      <c r="G22" s="23" t="s">
+      <c r="G22" s="22" t="s">
         <v>109</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="K22" s="27" t="s">
+      <c r="K22" s="26" t="s">
         <v>131</v>
       </c>
       <c r="L22" s="3" t="s">
@@ -5260,149 +5421,159 @@
       </c>
     </row>
     <row r="23" spans="7:12" ht="93.75" x14ac:dyDescent="0.25">
-      <c r="G23" s="23" t="s">
+      <c r="G23" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="H23" s="14" t="s">
+      <c r="H23" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="K23" s="27" t="s">
+      <c r="K23" s="26" t="s">
         <v>132</v>
       </c>
-      <c r="L23" s="14" t="s">
+      <c r="L23" s="13" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
-      <c r="K24" s="15"/>
-      <c r="L24" s="15"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
     </row>
     <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G25" s="24"/>
-      <c r="H25" s="24"/>
-      <c r="K25" s="24"/>
-      <c r="L25" s="24"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="23"/>
+      <c r="K25" s="23"/>
+      <c r="L25" s="23"/>
     </row>
     <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G26" s="24"/>
-      <c r="H26" s="24"/>
-      <c r="K26" s="24"/>
-      <c r="L26" s="24"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="23"/>
+      <c r="K26" s="23"/>
+      <c r="L26" s="23"/>
     </row>
     <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G27" s="24"/>
-      <c r="H27" s="24"/>
-      <c r="K27" s="24"/>
-      <c r="L27" s="24"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
+      <c r="K27" s="23"/>
+      <c r="L27" s="23"/>
     </row>
     <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G28" s="24"/>
-      <c r="H28" s="24"/>
-      <c r="K28" s="24"/>
-      <c r="L28" s="24"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
     </row>
     <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G29" s="24"/>
-      <c r="H29" s="24"/>
-      <c r="K29" s="24"/>
-      <c r="L29" s="24"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="23"/>
+      <c r="K29" s="23"/>
+      <c r="L29" s="23"/>
     </row>
     <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G30" s="24"/>
-      <c r="H30" s="24"/>
-      <c r="K30" s="24"/>
-      <c r="L30" s="24"/>
+      <c r="G30" s="23"/>
+      <c r="H30" s="23"/>
+      <c r="K30" s="23"/>
+      <c r="L30" s="23"/>
     </row>
     <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G31" s="24"/>
-      <c r="H31" s="24"/>
-      <c r="K31" s="24"/>
-      <c r="L31" s="24"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23"/>
+      <c r="K31" s="23"/>
+      <c r="L31" s="23"/>
     </row>
     <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G32" s="24"/>
-      <c r="H32" s="24"/>
-      <c r="K32" s="24"/>
-      <c r="L32" s="24"/>
+      <c r="G32" s="23"/>
+      <c r="H32" s="23"/>
+      <c r="K32" s="23"/>
+      <c r="L32" s="23"/>
     </row>
     <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G33" s="16"/>
-      <c r="H33" s="16"/>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+      <c r="K33" s="15"/>
+      <c r="L33" s="15"/>
     </row>
     <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G34" s="16"/>
-      <c r="H34" s="16"/>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="15"/>
+      <c r="K34" s="15"/>
+      <c r="L34" s="15"/>
     </row>
     <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G35" s="16"/>
-      <c r="H35" s="16"/>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="15"/>
+      <c r="K35" s="15"/>
+      <c r="L35" s="15"/>
     </row>
     <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G36" s="16"/>
-      <c r="H36" s="16"/>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="15"/>
+      <c r="K36" s="15"/>
+      <c r="L36" s="15"/>
     </row>
     <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G37" s="16"/>
-      <c r="H37" s="16"/>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="15"/>
+      <c r="K37" s="15"/>
+      <c r="L37" s="15"/>
     </row>
     <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G38" s="16"/>
-      <c r="H38" s="16"/>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="15"/>
+      <c r="K38" s="15"/>
+      <c r="L38" s="15"/>
     </row>
     <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G39" s="16"/>
-      <c r="H39" s="16"/>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="15"/>
+      <c r="K39" s="15"/>
+      <c r="L39" s="15"/>
     </row>
     <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G40" s="16"/>
-      <c r="H40" s="16"/>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
+      <c r="G40" s="15"/>
+      <c r="H40" s="15"/>
+      <c r="K40" s="15"/>
+      <c r="L40" s="15"/>
     </row>
     <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G41" s="16"/>
-      <c r="H41" s="16"/>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
+      <c r="G41" s="15"/>
+      <c r="H41" s="15"/>
+      <c r="K41" s="15"/>
+      <c r="L41" s="15"/>
     </row>
     <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G42" s="16"/>
-      <c r="H42" s="16"/>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
+      <c r="G42" s="15"/>
+      <c r="H42" s="15"/>
+      <c r="K42" s="15"/>
+      <c r="L42" s="15"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54428EA1-B8FA-4CDC-9D60-36F1167331A2}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="46" t="s">
+        <v>175</v>
+      </c>
+      <c r="C2" s="47"/>
+      <c r="D2" s="48"/>
       <c r="G2" s="4" t="s">
         <v>84</v>
       </c>
@@ -5416,196 +5587,252 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G3" s="38" t="s">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="49" t="s">
+        <v>182</v>
+      </c>
+      <c r="C3" s="50"/>
+      <c r="D3" s="51"/>
+      <c r="G3" s="37" t="s">
         <v>133</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K3" s="29" t="s">
+      <c r="K3" s="28" t="s">
         <v>119</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>178</v>
+      </c>
       <c r="G4" s="2" t="s">
         <v>134</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K4" s="18" t="s">
+      <c r="K4" s="17" t="s">
         <v>131</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G5" s="18" t="s">
+    <row r="5" spans="2:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="B5" s="52" t="s">
+        <v>179</v>
+      </c>
+      <c r="C5" s="52" t="s">
+        <v>179</v>
+      </c>
+      <c r="D5" s="52" t="s">
+        <v>183</v>
+      </c>
+      <c r="G5" s="17" t="s">
         <v>103</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K5" s="18" t="s">
+      <c r="K5" s="17" t="s">
         <v>123</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G6" s="28" t="s">
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="15"/>
+      <c r="G6" s="27" t="s">
         <v>135</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K6" s="18" t="s">
+      <c r="K6" s="17" t="s">
         <v>128</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G7" s="19" t="s">
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="53"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="15"/>
+      <c r="G7" s="18" t="s">
         <v>93</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K7" s="18" t="s">
+      <c r="K7" s="17" t="s">
         <v>129</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G8" s="19" t="s">
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="15"/>
+      <c r="G8" s="18" t="s">
         <v>95</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K8" s="28" t="s">
+      <c r="K8" s="27" t="s">
         <v>139</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G9" s="19" t="s">
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="53"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="15"/>
+      <c r="G9" s="18" t="s">
         <v>102</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K9" s="28" t="s">
+      <c r="K9" s="27" t="s">
         <v>118</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G10" s="19" t="s">
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="53"/>
+      <c r="C10" s="53"/>
+      <c r="D10" s="15"/>
+      <c r="G10" s="18" t="s">
         <v>88</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K10" s="28" t="s">
+      <c r="K10" s="27" t="s">
         <v>124</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G11" s="19" t="s">
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="15"/>
+      <c r="G11" s="18" t="s">
         <v>90</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K11" s="28" t="s">
+      <c r="K11" s="27" t="s">
         <v>121</v>
       </c>
       <c r="L11" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G12" s="19" t="s">
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="53"/>
+      <c r="C12" s="53"/>
+      <c r="D12" s="15"/>
+      <c r="G12" s="18" t="s">
         <v>91</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K12" s="28" t="s">
+      <c r="K12" s="27" t="s">
         <v>120</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G13" s="19" t="s">
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="53"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="15"/>
+      <c r="G13" s="18" t="s">
         <v>136</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K13" s="28" t="s">
+      <c r="K13" s="27" t="s">
         <v>130</v>
       </c>
       <c r="L13" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G14" s="19" t="s">
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="15"/>
+      <c r="G14" s="18" t="s">
         <v>98</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K14" s="19" t="s">
+      <c r="K14" s="18" t="s">
         <v>127</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G15" s="22" t="s">
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="53"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="15"/>
+      <c r="G15" s="21" t="s">
         <v>137</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K15" s="19" t="s">
+      <c r="K15" s="18" t="s">
         <v>140</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G16" s="22" t="s">
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="53"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="15"/>
+      <c r="G16" s="21" t="s">
         <v>94</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K16" s="19" t="s">
+      <c r="K16" s="18" t="s">
         <v>141</v>
       </c>
       <c r="L16" s="3" t="s">
@@ -5613,13 +5840,13 @@
       </c>
     </row>
     <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G17" s="27" t="s">
+      <c r="G17" s="26" t="s">
         <v>138</v>
       </c>
-      <c r="H17" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="K17" s="19" t="s">
+      <c r="H17" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="K17" s="18" t="s">
         <v>117</v>
       </c>
       <c r="L17" s="3" t="s">
@@ -5627,9 +5854,9 @@
       </c>
     </row>
     <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="K18" s="19" t="s">
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="K18" s="18" t="s">
         <v>142</v>
       </c>
       <c r="L18" s="3" t="s">
@@ -5637,9 +5864,9 @@
       </c>
     </row>
     <row r="19" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G19" s="24"/>
-      <c r="H19" s="24"/>
-      <c r="K19" s="20" t="s">
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
+      <c r="K19" s="19" t="s">
         <v>122</v>
       </c>
       <c r="L19" s="3" t="s">
@@ -5647,9 +5874,9 @@
       </c>
     </row>
     <row r="20" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G20" s="24"/>
-      <c r="H20" s="24"/>
-      <c r="K20" s="20" t="s">
+      <c r="G20" s="23"/>
+      <c r="H20" s="23"/>
+      <c r="K20" s="19" t="s">
         <v>143</v>
       </c>
       <c r="L20" s="3" t="s">
@@ -5657,19 +5884,19 @@
       </c>
     </row>
     <row r="21" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
-      <c r="K21" s="23" t="s">
+      <c r="G21" s="23"/>
+      <c r="H21" s="23"/>
+      <c r="K21" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="L21" s="14" t="s">
+      <c r="L21" s="13" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="22" spans="7:12" ht="150" x14ac:dyDescent="0.25">
-      <c r="G22" s="24"/>
-      <c r="H22" s="24"/>
-      <c r="K22" s="30" t="s">
+      <c r="G22" s="23"/>
+      <c r="H22" s="23"/>
+      <c r="K22" s="29" t="s">
         <v>145</v>
       </c>
       <c r="L22" s="2" t="s">
@@ -5677,141 +5904,151 @@
       </c>
     </row>
     <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G23" s="24"/>
-      <c r="H23" s="24"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="24"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="23"/>
+      <c r="K23" s="23"/>
+      <c r="L23" s="23"/>
     </row>
     <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G24" s="24"/>
-      <c r="H24" s="24"/>
-      <c r="K24" s="24"/>
-      <c r="L24" s="24"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="23"/>
+      <c r="K24" s="23"/>
+      <c r="L24" s="23"/>
     </row>
     <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G25" s="24"/>
-      <c r="H25" s="24"/>
-      <c r="K25" s="24"/>
-      <c r="L25" s="24"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="23"/>
+      <c r="K25" s="23"/>
+      <c r="L25" s="23"/>
     </row>
     <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G26" s="24"/>
-      <c r="H26" s="24"/>
-      <c r="K26" s="24"/>
-      <c r="L26" s="24"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="23"/>
+      <c r="K26" s="23"/>
+      <c r="L26" s="23"/>
     </row>
     <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G27" s="24"/>
-      <c r="H27" s="24"/>
-      <c r="K27" s="24"/>
-      <c r="L27" s="24"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
+      <c r="K27" s="23"/>
+      <c r="L27" s="23"/>
     </row>
     <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G28" s="24"/>
-      <c r="H28" s="24"/>
-      <c r="K28" s="24"/>
-      <c r="L28" s="24"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
     </row>
     <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G29" s="24"/>
-      <c r="H29" s="24"/>
-      <c r="K29" s="24"/>
-      <c r="L29" s="24"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="23"/>
+      <c r="K29" s="23"/>
+      <c r="L29" s="23"/>
     </row>
     <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G30" s="24"/>
-      <c r="H30" s="24"/>
-      <c r="K30" s="24"/>
-      <c r="L30" s="24"/>
+      <c r="G30" s="23"/>
+      <c r="H30" s="23"/>
+      <c r="K30" s="23"/>
+      <c r="L30" s="23"/>
     </row>
     <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G31" s="24"/>
-      <c r="H31" s="24"/>
-      <c r="K31" s="24"/>
-      <c r="L31" s="24"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23"/>
+      <c r="K31" s="23"/>
+      <c r="L31" s="23"/>
     </row>
     <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G32" s="24"/>
-      <c r="H32" s="24"/>
-      <c r="K32" s="24"/>
-      <c r="L32" s="24"/>
+      <c r="G32" s="23"/>
+      <c r="H32" s="23"/>
+      <c r="K32" s="23"/>
+      <c r="L32" s="23"/>
     </row>
     <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G33" s="16"/>
-      <c r="H33" s="16"/>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+      <c r="K33" s="15"/>
+      <c r="L33" s="15"/>
     </row>
     <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G34" s="16"/>
-      <c r="H34" s="16"/>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="15"/>
+      <c r="K34" s="15"/>
+      <c r="L34" s="15"/>
     </row>
     <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G35" s="16"/>
-      <c r="H35" s="16"/>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="15"/>
+      <c r="K35" s="15"/>
+      <c r="L35" s="15"/>
     </row>
     <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G36" s="16"/>
-      <c r="H36" s="16"/>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="15"/>
+      <c r="K36" s="15"/>
+      <c r="L36" s="15"/>
     </row>
     <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G37" s="16"/>
-      <c r="H37" s="16"/>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="15"/>
+      <c r="K37" s="15"/>
+      <c r="L37" s="15"/>
     </row>
     <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G38" s="16"/>
-      <c r="H38" s="16"/>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="15"/>
+      <c r="K38" s="15"/>
+      <c r="L38" s="15"/>
     </row>
     <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G39" s="16"/>
-      <c r="H39" s="16"/>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="15"/>
+      <c r="K39" s="15"/>
+      <c r="L39" s="15"/>
     </row>
     <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G40" s="16"/>
-      <c r="H40" s="16"/>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
+      <c r="G40" s="15"/>
+      <c r="H40" s="15"/>
+      <c r="K40" s="15"/>
+      <c r="L40" s="15"/>
     </row>
     <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G41" s="16"/>
-      <c r="H41" s="16"/>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
+      <c r="G41" s="15"/>
+      <c r="H41" s="15"/>
+      <c r="K41" s="15"/>
+      <c r="L41" s="15"/>
     </row>
     <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G42" s="16"/>
-      <c r="H42" s="16"/>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
+      <c r="G42" s="15"/>
+      <c r="H42" s="15"/>
+      <c r="K42" s="15"/>
+      <c r="L42" s="15"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EA9158E-5B25-4659-9455-CB16792B33F3}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="46" t="s">
+        <v>175</v>
+      </c>
+      <c r="C2" s="47"/>
+      <c r="D2" s="48"/>
       <c r="G2" s="4" t="s">
         <v>84</v>
       </c>
@@ -5825,196 +6062,252 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G3" s="17" t="s">
+    <row r="3" spans="2:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="49" t="s">
+        <v>182</v>
+      </c>
+      <c r="C3" s="50"/>
+      <c r="D3" s="51"/>
+      <c r="G3" s="16" t="s">
         <v>86</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="K3" s="32" t="s">
+      <c r="K3" s="31" t="s">
         <v>119</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>178</v>
+      </c>
       <c r="G4" s="2" t="s">
         <v>134</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="K4" s="19" t="s">
+      <c r="K4" s="18" t="s">
         <v>121</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G5" s="19" t="s">
+    <row r="5" spans="2:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="B5" s="52" t="s">
+        <v>179</v>
+      </c>
+      <c r="C5" s="52" t="s">
+        <v>179</v>
+      </c>
+      <c r="D5" s="52" t="s">
+        <v>183</v>
+      </c>
+      <c r="G5" s="18" t="s">
         <v>135</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="K5" s="19" t="s">
+      <c r="K5" s="18" t="s">
         <v>127</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G6" s="19" t="s">
+    <row r="6" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="15"/>
+      <c r="G6" s="18" t="s">
         <v>88</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="K6" s="19" t="s">
+      <c r="K6" s="18" t="s">
         <v>141</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G7" s="19" t="s">
+    <row r="7" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B7" s="53"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="15"/>
+      <c r="G7" s="18" t="s">
         <v>105</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="K7" s="19" t="s">
+      <c r="K7" s="18" t="s">
         <v>142</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G8" s="19" t="s">
+    <row r="8" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="15"/>
+      <c r="G8" s="18" t="s">
         <v>136</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="K8" s="19" t="s">
+      <c r="K8" s="18" t="s">
         <v>117</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G9" s="19" t="s">
+    <row r="9" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B9" s="53"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="15"/>
+      <c r="G9" s="18" t="s">
         <v>98</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="K9" s="19" t="s">
+      <c r="K9" s="18" t="s">
         <v>118</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G10" s="19" t="s">
+    <row r="10" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B10" s="53"/>
+      <c r="C10" s="53"/>
+      <c r="D10" s="15"/>
+      <c r="G10" s="18" t="s">
         <v>94</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="K10" s="19" t="s">
+      <c r="K10" s="18" t="s">
         <v>124</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G11" s="22" t="s">
+    <row r="11" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="15"/>
+      <c r="G11" s="21" t="s">
         <v>137</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="K11" s="19" t="s">
+      <c r="K11" s="18" t="s">
         <v>140</v>
       </c>
       <c r="L11" s="3" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G12" s="22" t="s">
+    <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B12" s="53"/>
+      <c r="C12" s="53"/>
+      <c r="D12" s="15"/>
+      <c r="G12" s="21" t="s">
         <v>102</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="K12" s="19" t="s">
+      <c r="K12" s="18" t="s">
         <v>120</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G13" s="22" t="s">
+    <row r="13" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B13" s="53"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="15"/>
+      <c r="G13" s="21" t="s">
         <v>99</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="K13" s="19" t="s">
+      <c r="K13" s="18" t="s">
         <v>149</v>
       </c>
       <c r="L13" s="3" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G14" s="20" t="s">
+    <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="15"/>
+      <c r="G14" s="19" t="s">
         <v>91</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="K14" s="22" t="s">
+      <c r="K14" s="21" t="s">
         <v>128</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G15" s="20" t="s">
+    <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B15" s="53"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="15"/>
+      <c r="G15" s="19" t="s">
         <v>108</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="K15" s="22" t="s">
+      <c r="K15" s="21" t="s">
         <v>129</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G16" s="20" t="s">
+    <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B16" s="53"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="15"/>
+      <c r="G16" s="19" t="s">
         <v>138</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="K16" s="22" t="s">
+      <c r="K16" s="21" t="s">
         <v>115</v>
       </c>
       <c r="L16" s="3" t="s">
@@ -6022,13 +6315,13 @@
       </c>
     </row>
     <row r="17" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G17" s="20" t="s">
+      <c r="G17" s="19" t="s">
         <v>96</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="K17" s="22" t="s">
+      <c r="K17" s="21" t="s">
         <v>122</v>
       </c>
       <c r="L17" s="3" t="s">
@@ -6036,13 +6329,13 @@
       </c>
     </row>
     <row r="18" spans="7:12" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="G18" s="31" t="s">
+      <c r="G18" s="30" t="s">
         <v>148</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="K18" s="22" t="s">
+      <c r="K18" s="21" t="s">
         <v>125</v>
       </c>
       <c r="L18" s="3" t="s">
@@ -6050,9 +6343,9 @@
       </c>
     </row>
     <row r="19" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="K19" s="22" t="s">
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="K19" s="21" t="s">
         <v>130</v>
       </c>
       <c r="L19" s="3" t="s">
@@ -6060,9 +6353,9 @@
       </c>
     </row>
     <row r="20" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G20" s="24"/>
-      <c r="H20" s="24"/>
-      <c r="K20" s="22" t="s">
+      <c r="G20" s="23"/>
+      <c r="H20" s="23"/>
+      <c r="K20" s="21" t="s">
         <v>126</v>
       </c>
       <c r="L20" s="3" t="s">
@@ -6070,9 +6363,9 @@
       </c>
     </row>
     <row r="21" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
-      <c r="K21" s="22" t="s">
+      <c r="G21" s="23"/>
+      <c r="H21" s="23"/>
+      <c r="K21" s="21" t="s">
         <v>143</v>
       </c>
       <c r="L21" s="3" t="s">
@@ -6080,9 +6373,9 @@
       </c>
     </row>
     <row r="22" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G22" s="24"/>
-      <c r="H22" s="24"/>
-      <c r="K22" s="45" t="s">
+      <c r="G22" s="23"/>
+      <c r="H22" s="23"/>
+      <c r="K22" s="44" t="s">
         <v>116</v>
       </c>
       <c r="L22" s="3" t="s">
@@ -6090,141 +6383,151 @@
       </c>
     </row>
     <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G23" s="24"/>
-      <c r="H23" s="24"/>
-      <c r="K23" s="15"/>
-      <c r="L23" s="15"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="23"/>
+      <c r="K23" s="14"/>
+      <c r="L23" s="14"/>
     </row>
     <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G24" s="24"/>
-      <c r="H24" s="24"/>
-      <c r="K24" s="24"/>
-      <c r="L24" s="24"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="23"/>
+      <c r="K24" s="23"/>
+      <c r="L24" s="23"/>
     </row>
     <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G25" s="24"/>
-      <c r="H25" s="24"/>
-      <c r="K25" s="24"/>
-      <c r="L25" s="24"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="23"/>
+      <c r="K25" s="23"/>
+      <c r="L25" s="23"/>
     </row>
     <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G26" s="24"/>
-      <c r="H26" s="24"/>
-      <c r="K26" s="24"/>
-      <c r="L26" s="24"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="23"/>
+      <c r="K26" s="23"/>
+      <c r="L26" s="23"/>
     </row>
     <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G27" s="24"/>
-      <c r="H27" s="24"/>
-      <c r="K27" s="24"/>
-      <c r="L27" s="24"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
+      <c r="K27" s="23"/>
+      <c r="L27" s="23"/>
     </row>
     <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G28" s="24"/>
-      <c r="H28" s="24"/>
-      <c r="K28" s="24"/>
-      <c r="L28" s="24"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
     </row>
     <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G29" s="24"/>
-      <c r="H29" s="24"/>
-      <c r="K29" s="24"/>
-      <c r="L29" s="24"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="23"/>
+      <c r="K29" s="23"/>
+      <c r="L29" s="23"/>
     </row>
     <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G30" s="24"/>
-      <c r="H30" s="24"/>
-      <c r="K30" s="24"/>
-      <c r="L30" s="24"/>
+      <c r="G30" s="23"/>
+      <c r="H30" s="23"/>
+      <c r="K30" s="23"/>
+      <c r="L30" s="23"/>
     </row>
     <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G31" s="24"/>
-      <c r="H31" s="24"/>
-      <c r="K31" s="24"/>
-      <c r="L31" s="24"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23"/>
+      <c r="K31" s="23"/>
+      <c r="L31" s="23"/>
     </row>
     <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G32" s="24"/>
-      <c r="H32" s="24"/>
-      <c r="K32" s="24"/>
-      <c r="L32" s="24"/>
+      <c r="G32" s="23"/>
+      <c r="H32" s="23"/>
+      <c r="K32" s="23"/>
+      <c r="L32" s="23"/>
     </row>
     <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G33" s="16"/>
-      <c r="H33" s="16"/>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+      <c r="K33" s="15"/>
+      <c r="L33" s="15"/>
     </row>
     <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G34" s="16"/>
-      <c r="H34" s="16"/>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="15"/>
+      <c r="K34" s="15"/>
+      <c r="L34" s="15"/>
     </row>
     <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G35" s="16"/>
-      <c r="H35" s="16"/>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="15"/>
+      <c r="K35" s="15"/>
+      <c r="L35" s="15"/>
     </row>
     <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G36" s="16"/>
-      <c r="H36" s="16"/>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="15"/>
+      <c r="K36" s="15"/>
+      <c r="L36" s="15"/>
     </row>
     <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G37" s="16"/>
-      <c r="H37" s="16"/>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="15"/>
+      <c r="K37" s="15"/>
+      <c r="L37" s="15"/>
     </row>
     <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G38" s="16"/>
-      <c r="H38" s="16"/>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="15"/>
+      <c r="K38" s="15"/>
+      <c r="L38" s="15"/>
     </row>
     <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G39" s="16"/>
-      <c r="H39" s="16"/>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="15"/>
+      <c r="K39" s="15"/>
+      <c r="L39" s="15"/>
     </row>
     <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G40" s="16"/>
-      <c r="H40" s="16"/>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
+      <c r="G40" s="15"/>
+      <c r="H40" s="15"/>
+      <c r="K40" s="15"/>
+      <c r="L40" s="15"/>
     </row>
     <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G41" s="16"/>
-      <c r="H41" s="16"/>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
+      <c r="G41" s="15"/>
+      <c r="H41" s="15"/>
+      <c r="K41" s="15"/>
+      <c r="L41" s="15"/>
     </row>
     <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G42" s="16"/>
-      <c r="H42" s="16"/>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
+      <c r="G42" s="15"/>
+      <c r="H42" s="15"/>
+      <c r="K42" s="15"/>
+      <c r="L42" s="15"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8F06796-6B63-4D23-8399-5C2D3A86CDB8}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="46" t="s">
+        <v>175</v>
+      </c>
+      <c r="C2" s="47"/>
+      <c r="D2" s="48"/>
       <c r="G2" s="4" t="s">
         <v>84</v>
       </c>
@@ -6238,196 +6541,252 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G3" s="34" t="s">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="49" t="s">
+        <v>184</v>
+      </c>
+      <c r="C3" s="50"/>
+      <c r="D3" s="51"/>
+      <c r="G3" s="33" t="s">
         <v>134</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K3" s="33" t="s">
+      <c r="K3" s="32" t="s">
         <v>113</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G4" s="40" t="s">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="G4" s="39" t="s">
         <v>151</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K4" s="26" t="s">
+      <c r="K4" s="25" t="s">
         <v>127</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G5" s="35" t="s">
+    <row r="5" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="B5" s="52" t="s">
+        <v>179</v>
+      </c>
+      <c r="C5" s="52" t="s">
+        <v>185</v>
+      </c>
+      <c r="D5" s="52" t="s">
+        <v>186</v>
+      </c>
+      <c r="G5" s="34" t="s">
         <v>91</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K5" s="26" t="s">
+      <c r="K5" s="25" t="s">
         <v>119</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G6" s="22" t="s">
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="15"/>
+      <c r="G6" s="21" t="s">
         <v>88</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K6" s="26" t="s">
+      <c r="K6" s="25" t="s">
         <v>125</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G7" s="22" t="s">
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="53"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="15"/>
+      <c r="G7" s="21" t="s">
         <v>90</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K7" s="26" t="s">
+      <c r="K7" s="25" t="s">
         <v>143</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G8" s="26" t="s">
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="15"/>
+      <c r="G8" s="25" t="s">
         <v>135</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K8" s="26" t="s">
+      <c r="K8" s="25" t="s">
         <v>117</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G9" s="26" t="s">
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="53"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="15"/>
+      <c r="G9" s="25" t="s">
         <v>102</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K9" s="26" t="s">
+      <c r="K9" s="25" t="s">
         <v>140</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G10" s="42" t="s">
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="53"/>
+      <c r="C10" s="53"/>
+      <c r="D10" s="15"/>
+      <c r="G10" s="41" t="s">
         <v>105</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K10" s="26" t="s">
+      <c r="K10" s="25" t="s">
         <v>122</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G11" s="26" t="s">
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="15"/>
+      <c r="G11" s="25" t="s">
         <v>138</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K11" s="26" t="s">
+      <c r="K11" s="25" t="s">
         <v>118</v>
       </c>
       <c r="L11" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G12" s="26" t="s">
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="53"/>
+      <c r="C12" s="53"/>
+      <c r="D12" s="15"/>
+      <c r="G12" s="25" t="s">
         <v>108</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K12" s="26" t="s">
+      <c r="K12" s="25" t="s">
         <v>149</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G13" s="26" t="s">
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="53"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="15"/>
+      <c r="G13" s="25" t="s">
         <v>152</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K13" s="26" t="s">
+      <c r="K13" s="25" t="s">
         <v>120</v>
       </c>
       <c r="L13" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G14" s="42" t="s">
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="15"/>
+      <c r="G14" s="41" t="s">
         <v>153</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K14" s="26" t="s">
+      <c r="K14" s="25" t="s">
         <v>142</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G15" s="26" t="s">
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="53"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="15"/>
+      <c r="G15" s="25" t="s">
         <v>96</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K15" s="26" t="s">
+      <c r="K15" s="25" t="s">
         <v>121</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G16" s="26" t="s">
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="53"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="15"/>
+      <c r="G16" s="25" t="s">
         <v>99</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K16" s="26" t="s">
+      <c r="K16" s="25" t="s">
         <v>124</v>
       </c>
       <c r="L16" s="3" t="s">
@@ -6435,13 +6794,13 @@
       </c>
     </row>
     <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G17" s="26" t="s">
+      <c r="G17" s="25" t="s">
         <v>154</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K17" s="20" t="s">
+      <c r="K17" s="19" t="s">
         <v>128</v>
       </c>
       <c r="L17" s="3" t="s">
@@ -6449,13 +6808,13 @@
       </c>
     </row>
     <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G18" s="26" t="s">
+      <c r="G18" s="25" t="s">
         <v>155</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K18" s="20" t="s">
+      <c r="K18" s="19" t="s">
         <v>129</v>
       </c>
       <c r="L18" s="3" t="s">
@@ -6463,13 +6822,13 @@
       </c>
     </row>
     <row r="19" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G19" s="42" t="s">
+      <c r="G19" s="41" t="s">
         <v>156</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K19" s="20" t="s">
+      <c r="K19" s="19" t="s">
         <v>130</v>
       </c>
       <c r="L19" s="3" t="s">
@@ -6477,13 +6836,13 @@
       </c>
     </row>
     <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G20" s="20" t="s">
+      <c r="G20" s="19" t="s">
         <v>89</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K20" s="18" t="s">
+      <c r="K20" s="17" t="s">
         <v>131</v>
       </c>
       <c r="L20" s="3" t="s">
@@ -6491,13 +6850,13 @@
       </c>
     </row>
     <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G21" s="20" t="s">
+      <c r="G21" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="H21" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="K21" s="18" t="s">
+      <c r="H21" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="K21" s="17" t="s">
         <v>123</v>
       </c>
       <c r="L21" s="3" t="s">
@@ -6505,177 +6864,187 @@
       </c>
     </row>
     <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G22" s="18" t="s">
+      <c r="G22" s="17" t="s">
         <v>137</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K22" s="36" t="s">
+      <c r="K22" s="35" t="s">
         <v>145</v>
       </c>
-      <c r="L22" s="14" t="s">
+      <c r="L22" s="13" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G23" s="18" t="s">
+      <c r="G23" s="17" t="s">
         <v>110</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K23" s="15"/>
-      <c r="L23" s="15"/>
+      <c r="K23" s="14"/>
+      <c r="L23" s="14"/>
     </row>
     <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G24" s="18" t="s">
+      <c r="G24" s="17" t="s">
         <v>101</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K24" s="24"/>
-      <c r="L24" s="24"/>
+      <c r="K24" s="23"/>
+      <c r="L24" s="23"/>
     </row>
     <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G25" s="18" t="s">
+      <c r="G25" s="17" t="s">
         <v>94</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K25" s="24"/>
-      <c r="L25" s="24"/>
+      <c r="K25" s="23"/>
+      <c r="L25" s="23"/>
     </row>
     <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G26" s="36" t="s">
+      <c r="G26" s="35" t="s">
         <v>109</v>
       </c>
-      <c r="H26" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="K26" s="24"/>
-      <c r="L26" s="24"/>
+      <c r="H26" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="K26" s="23"/>
+      <c r="L26" s="23"/>
     </row>
     <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G27" s="20" t="s">
+      <c r="G27" s="19" t="s">
         <v>158</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="K27" s="24"/>
-      <c r="L27" s="24"/>
+      <c r="K27" s="23"/>
+      <c r="L27" s="23"/>
     </row>
     <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G28" s="42" t="s">
+      <c r="G28" s="41" t="s">
         <v>157</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="K28" s="24"/>
-      <c r="L28" s="24"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
     </row>
     <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="K29" s="24"/>
-      <c r="L29" s="24"/>
+      <c r="K29" s="23"/>
+      <c r="L29" s="23"/>
     </row>
     <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G30" s="24"/>
-      <c r="H30" s="24"/>
-      <c r="K30" s="24"/>
-      <c r="L30" s="24"/>
+      <c r="G30" s="23"/>
+      <c r="H30" s="23"/>
+      <c r="K30" s="23"/>
+      <c r="L30" s="23"/>
     </row>
     <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G31" s="24"/>
-      <c r="H31" s="24"/>
-      <c r="K31" s="24"/>
-      <c r="L31" s="24"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23"/>
+      <c r="K31" s="23"/>
+      <c r="L31" s="23"/>
     </row>
     <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G32" s="24"/>
-      <c r="H32" s="24"/>
-      <c r="K32" s="24"/>
-      <c r="L32" s="24"/>
+      <c r="G32" s="23"/>
+      <c r="H32" s="23"/>
+      <c r="K32" s="23"/>
+      <c r="L32" s="23"/>
     </row>
     <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G33" s="16"/>
-      <c r="H33" s="16"/>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+      <c r="K33" s="15"/>
+      <c r="L33" s="15"/>
     </row>
     <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G34" s="16"/>
-      <c r="H34" s="16"/>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="15"/>
+      <c r="K34" s="15"/>
+      <c r="L34" s="15"/>
     </row>
     <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G35" s="16"/>
-      <c r="H35" s="16"/>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="15"/>
+      <c r="K35" s="15"/>
+      <c r="L35" s="15"/>
     </row>
     <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G36" s="16"/>
-      <c r="H36" s="16"/>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="15"/>
+      <c r="K36" s="15"/>
+      <c r="L36" s="15"/>
     </row>
     <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G37" s="16"/>
-      <c r="H37" s="16"/>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="15"/>
+      <c r="K37" s="15"/>
+      <c r="L37" s="15"/>
     </row>
     <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G38" s="16"/>
-      <c r="H38" s="16"/>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="15"/>
+      <c r="K38" s="15"/>
+      <c r="L38" s="15"/>
     </row>
     <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G39" s="16"/>
-      <c r="H39" s="16"/>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="15"/>
+      <c r="K39" s="15"/>
+      <c r="L39" s="15"/>
     </row>
     <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G40" s="16"/>
-      <c r="H40" s="16"/>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
+      <c r="G40" s="15"/>
+      <c r="H40" s="15"/>
+      <c r="K40" s="15"/>
+      <c r="L40" s="15"/>
     </row>
     <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G41" s="16"/>
-      <c r="H41" s="16"/>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
+      <c r="G41" s="15"/>
+      <c r="H41" s="15"/>
+      <c r="K41" s="15"/>
+      <c r="L41" s="15"/>
     </row>
     <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G42" s="16"/>
-      <c r="H42" s="16"/>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
+      <c r="G42" s="15"/>
+      <c r="H42" s="15"/>
+      <c r="K42" s="15"/>
+      <c r="L42" s="15"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66C252C5-A4A0-46E4-AF3D-69F9DB4F2D8C}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="46" t="s">
+        <v>175</v>
+      </c>
+      <c r="C2" s="47"/>
+      <c r="D2" s="48"/>
       <c r="G2" s="4" t="s">
         <v>84</v>
       </c>
@@ -6689,196 +7058,252 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G3" s="17" t="s">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="49" t="s">
+        <v>187</v>
+      </c>
+      <c r="C3" s="50"/>
+      <c r="D3" s="51"/>
+      <c r="G3" s="16" t="s">
         <v>87</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K3" s="33" t="s">
+      <c r="K3" s="32" t="s">
         <v>119</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G4" s="35" t="s">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="G4" s="34" t="s">
         <v>135</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K4" s="22" t="s">
+      <c r="K4" s="21" t="s">
         <v>118</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G5" s="35" t="s">
+    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="52" t="s">
+        <v>180</v>
+      </c>
+      <c r="C5" s="52" t="s">
+        <v>180</v>
+      </c>
+      <c r="D5" s="52" t="s">
+        <v>180</v>
+      </c>
+      <c r="G5" s="34" t="s">
         <v>161</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K5" s="22" t="s">
+      <c r="K5" s="21" t="s">
         <v>139</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G6" s="22" t="s">
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="15"/>
+      <c r="G6" s="21" t="s">
         <v>162</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K6" s="22" t="s">
+      <c r="K6" s="21" t="s">
         <v>123</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G7" s="22" t="s">
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="53"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="15"/>
+      <c r="G7" s="21" t="s">
         <v>110</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K7" s="46" t="s">
+      <c r="K7" s="45" t="s">
         <v>170</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G8" s="22" t="s">
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="15"/>
+      <c r="G8" s="21" t="s">
         <v>108</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K8" s="22" t="s">
+      <c r="K8" s="21" t="s">
         <v>171</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G9" s="22" t="s">
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="53"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="15"/>
+      <c r="G9" s="21" t="s">
         <v>101</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K9" s="22" t="s">
+      <c r="K9" s="21" t="s">
         <v>131</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G10" s="22" t="s">
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="53"/>
+      <c r="C10" s="53"/>
+      <c r="D10" s="15"/>
+      <c r="G10" s="21" t="s">
         <v>154</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K10" s="22" t="s">
+      <c r="K10" s="21" t="s">
         <v>130</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G11" s="22" t="s">
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="15"/>
+      <c r="G11" s="21" t="s">
         <v>155</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K11" s="22" t="s">
+      <c r="K11" s="21" t="s">
         <v>132</v>
       </c>
       <c r="L11" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="G12" s="22" t="s">
+    <row r="12" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="B12" s="53"/>
+      <c r="C12" s="53"/>
+      <c r="D12" s="15"/>
+      <c r="G12" s="21" t="s">
         <v>103</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="K12" s="22" t="s">
+      <c r="K12" s="21" t="s">
         <v>172</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="75" x14ac:dyDescent="0.25">
-      <c r="G13" s="22" t="s">
+    <row r="13" spans="2:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="B13" s="53"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="15"/>
+      <c r="G13" s="21" t="s">
         <v>164</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="K13" s="22" t="s">
+      <c r="K13" s="21" t="s">
         <v>117</v>
       </c>
       <c r="L13" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="75" x14ac:dyDescent="0.25">
-      <c r="G14" s="22" t="s">
+    <row r="14" spans="2:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="15"/>
+      <c r="G14" s="21" t="s">
         <v>165</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="K14" s="22" t="s">
+      <c r="K14" s="21" t="s">
         <v>140</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G15" s="19" t="s">
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="53"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="15"/>
+      <c r="G15" s="18" t="s">
         <v>152</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K15" s="22" t="s">
+      <c r="K15" s="21" t="s">
         <v>125</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G16" s="41" t="s">
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="53"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="15"/>
+      <c r="G16" s="40" t="s">
         <v>167</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K16" s="22" t="s">
+      <c r="K16" s="21" t="s">
         <v>124</v>
       </c>
       <c r="L16" s="3" t="s">
@@ -6886,13 +7311,13 @@
       </c>
     </row>
     <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G17" s="41" t="s">
+      <c r="G17" s="40" t="s">
         <v>168</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K17" s="22" t="s">
+      <c r="K17" s="21" t="s">
         <v>141</v>
       </c>
       <c r="L17" s="3" t="s">
@@ -6900,13 +7325,13 @@
       </c>
     </row>
     <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G18" s="19" t="s">
+      <c r="G18" s="18" t="s">
         <v>109</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K18" s="22" t="s">
+      <c r="K18" s="21" t="s">
         <v>121</v>
       </c>
       <c r="L18" s="3" t="s">
@@ -6914,13 +7339,13 @@
       </c>
     </row>
     <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G19" s="41" t="s">
+      <c r="G19" s="40" t="s">
         <v>169</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K19" s="22" t="s">
+      <c r="K19" s="21" t="s">
         <v>122</v>
       </c>
       <c r="L19" s="3" t="s">
@@ -6928,13 +7353,13 @@
       </c>
     </row>
     <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G20" s="28" t="s">
+      <c r="G20" s="27" t="s">
         <v>90</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K20" s="22" t="s">
+      <c r="K20" s="21" t="s">
         <v>115</v>
       </c>
       <c r="L20" s="3" t="s">
@@ -6942,13 +7367,13 @@
       </c>
     </row>
     <row r="21" spans="7:12" ht="75" x14ac:dyDescent="0.25">
-      <c r="G21" s="18" t="s">
+      <c r="G21" s="17" t="s">
         <v>157</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="K21" s="22" t="s">
+      <c r="K21" s="21" t="s">
         <v>120</v>
       </c>
       <c r="L21" s="3" t="s">
@@ -6956,151 +7381,161 @@
       </c>
     </row>
     <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G22" s="24"/>
-      <c r="H22" s="24"/>
-      <c r="K22" s="23" t="s">
+      <c r="G22" s="23"/>
+      <c r="H22" s="23"/>
+      <c r="K22" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="L22" s="14" t="s">
+      <c r="L22" s="13" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G23" s="24"/>
-      <c r="H23" s="24"/>
-      <c r="K23" s="15"/>
-      <c r="L23" s="15"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="23"/>
+      <c r="K23" s="14"/>
+      <c r="L23" s="14"/>
     </row>
     <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G24" s="24"/>
-      <c r="H24" s="24"/>
-      <c r="K24" s="24"/>
-      <c r="L24" s="24"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="23"/>
+      <c r="K24" s="23"/>
+      <c r="L24" s="23"/>
     </row>
     <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G25" s="24"/>
-      <c r="H25" s="24"/>
-      <c r="K25" s="24"/>
-      <c r="L25" s="24"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="23"/>
+      <c r="K25" s="23"/>
+      <c r="L25" s="23"/>
     </row>
     <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G26" s="24"/>
-      <c r="H26" s="24"/>
-      <c r="K26" s="24"/>
-      <c r="L26" s="24"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="23"/>
+      <c r="K26" s="23"/>
+      <c r="L26" s="23"/>
     </row>
     <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G27" s="24"/>
-      <c r="H27" s="24"/>
-      <c r="K27" s="24"/>
-      <c r="L27" s="24"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
+      <c r="K27" s="23"/>
+      <c r="L27" s="23"/>
     </row>
     <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G28" s="24"/>
-      <c r="H28" s="24"/>
-      <c r="K28" s="24"/>
-      <c r="L28" s="24"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
     </row>
     <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G29" s="24"/>
-      <c r="H29" s="24"/>
-      <c r="K29" s="24"/>
-      <c r="L29" s="24"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="23"/>
+      <c r="K29" s="23"/>
+      <c r="L29" s="23"/>
     </row>
     <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G30" s="24"/>
-      <c r="H30" s="24"/>
-      <c r="K30" s="24"/>
-      <c r="L30" s="24"/>
+      <c r="G30" s="23"/>
+      <c r="H30" s="23"/>
+      <c r="K30" s="23"/>
+      <c r="L30" s="23"/>
     </row>
     <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G31" s="24"/>
-      <c r="H31" s="24"/>
-      <c r="K31" s="24"/>
-      <c r="L31" s="24"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23"/>
+      <c r="K31" s="23"/>
+      <c r="L31" s="23"/>
     </row>
     <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G32" s="24"/>
-      <c r="H32" s="24"/>
-      <c r="K32" s="24"/>
-      <c r="L32" s="24"/>
+      <c r="G32" s="23"/>
+      <c r="H32" s="23"/>
+      <c r="K32" s="23"/>
+      <c r="L32" s="23"/>
     </row>
     <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G33" s="16"/>
-      <c r="H33" s="16"/>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+      <c r="K33" s="15"/>
+      <c r="L33" s="15"/>
     </row>
     <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G34" s="16"/>
-      <c r="H34" s="16"/>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="15"/>
+      <c r="K34" s="15"/>
+      <c r="L34" s="15"/>
     </row>
     <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G35" s="16"/>
-      <c r="H35" s="16"/>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="15"/>
+      <c r="K35" s="15"/>
+      <c r="L35" s="15"/>
     </row>
     <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G36" s="16"/>
-      <c r="H36" s="16"/>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="15"/>
+      <c r="K36" s="15"/>
+      <c r="L36" s="15"/>
     </row>
     <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G37" s="16"/>
-      <c r="H37" s="16"/>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="15"/>
+      <c r="K37" s="15"/>
+      <c r="L37" s="15"/>
     </row>
     <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G38" s="16"/>
-      <c r="H38" s="16"/>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="15"/>
+      <c r="K38" s="15"/>
+      <c r="L38" s="15"/>
     </row>
     <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G39" s="16"/>
-      <c r="H39" s="16"/>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="15"/>
+      <c r="K39" s="15"/>
+      <c r="L39" s="15"/>
     </row>
     <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G40" s="16"/>
-      <c r="H40" s="16"/>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
+      <c r="G40" s="15"/>
+      <c r="H40" s="15"/>
+      <c r="K40" s="15"/>
+      <c r="L40" s="15"/>
     </row>
     <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G41" s="16"/>
-      <c r="H41" s="16"/>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
+      <c r="G41" s="15"/>
+      <c r="H41" s="15"/>
+      <c r="K41" s="15"/>
+      <c r="L41" s="15"/>
     </row>
     <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G42" s="16"/>
-      <c r="H42" s="16"/>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
+      <c r="G42" s="15"/>
+      <c r="H42" s="15"/>
+      <c r="K42" s="15"/>
+      <c r="L42" s="15"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84FA3A52-228B-4A13-B0AF-579CAC1203E1}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="46" t="s">
+        <v>175</v>
+      </c>
+      <c r="C2" s="47"/>
+      <c r="D2" s="48"/>
       <c r="G2" s="4" t="s">
         <v>84</v>
       </c>
@@ -7114,196 +7549,252 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G3" s="32" t="s">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="49" t="s">
+        <v>184</v>
+      </c>
+      <c r="C3" s="50"/>
+      <c r="D3" s="51"/>
+      <c r="G3" s="31" t="s">
         <v>135</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K3" s="32" t="s">
+      <c r="K3" s="31" t="s">
         <v>132</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G4" s="19" t="s">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="G4" s="18" t="s">
         <v>90</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K4" s="39" t="s">
+      <c r="K4" s="38" t="s">
         <v>172</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G5" s="19" t="s">
+    <row r="5" spans="2:12" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="52" t="s">
+        <v>179</v>
+      </c>
+      <c r="C5" s="52" t="s">
+        <v>179</v>
+      </c>
+      <c r="D5" s="52" t="s">
+        <v>186</v>
+      </c>
+      <c r="G5" s="18" t="s">
         <v>136</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K5" s="19" t="s">
+      <c r="K5" s="18" t="s">
         <v>127</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G6" s="19" t="s">
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="15"/>
+      <c r="G6" s="18" t="s">
         <v>93</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K6" s="19" t="s">
+      <c r="K6" s="18" t="s">
         <v>131</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G7" s="19" t="s">
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="53"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="15"/>
+      <c r="G7" s="18" t="s">
         <v>95</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K7" s="19" t="s">
+      <c r="K7" s="18" t="s">
         <v>119</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G8" s="19" t="s">
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="15"/>
+      <c r="G8" s="18" t="s">
         <v>103</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K8" s="19" t="s">
+      <c r="K8" s="18" t="s">
         <v>130</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G9" s="19" t="s">
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="53"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="15"/>
+      <c r="G9" s="18" t="s">
         <v>109</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K9" s="19" t="s">
+      <c r="K9" s="18" t="s">
         <v>141</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G10" s="19" t="s">
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="53"/>
+      <c r="C10" s="53"/>
+      <c r="D10" s="15"/>
+      <c r="G10" s="18" t="s">
         <v>173</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K10" s="19" t="s">
+      <c r="K10" s="18" t="s">
         <v>124</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G11" s="19" t="s">
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="15"/>
+      <c r="G11" s="18" t="s">
         <v>101</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K11" s="19" t="s">
+      <c r="K11" s="18" t="s">
         <v>118</v>
       </c>
       <c r="L11" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G12" s="41" t="s">
+    <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B12" s="53"/>
+      <c r="C12" s="53"/>
+      <c r="D12" s="15"/>
+      <c r="G12" s="40" t="s">
         <v>174</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K12" s="19" t="s">
+      <c r="K12" s="18" t="s">
         <v>149</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G13" s="19" t="s">
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="53"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="15"/>
+      <c r="G13" s="18" t="s">
         <v>161</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K13" s="19" t="s">
+      <c r="K13" s="18" t="s">
         <v>123</v>
       </c>
       <c r="L13" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G14" s="19" t="s">
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="15"/>
+      <c r="G14" s="18" t="s">
         <v>162</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K14" s="19" t="s">
+      <c r="K14" s="18" t="s">
         <v>125</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G15" s="20" t="s">
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="53"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="15"/>
+      <c r="G15" s="19" t="s">
         <v>108</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K15" s="19" t="s">
+      <c r="K15" s="18" t="s">
         <v>121</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G16" s="20" t="s">
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="53"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="15"/>
+      <c r="G16" s="19" t="s">
         <v>96</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K16" s="19" t="s">
+      <c r="K16" s="18" t="s">
         <v>140</v>
       </c>
       <c r="L16" s="3" t="s">
@@ -7311,13 +7802,13 @@
       </c>
     </row>
     <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G17" s="22" t="s">
+      <c r="G17" s="21" t="s">
         <v>102</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K17" s="19" t="s">
+      <c r="K17" s="18" t="s">
         <v>117</v>
       </c>
       <c r="L17" s="3" t="s">
@@ -7325,13 +7816,13 @@
       </c>
     </row>
     <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G18" s="22" t="s">
+      <c r="G18" s="21" t="s">
         <v>137</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K18" s="19" t="s">
+      <c r="K18" s="18" t="s">
         <v>142</v>
       </c>
       <c r="L18" s="3" t="s">
@@ -7339,13 +7830,13 @@
       </c>
     </row>
     <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G19" s="22" t="s">
+      <c r="G19" s="21" t="s">
         <v>154</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K19" s="22" t="s">
+      <c r="K19" s="21" t="s">
         <v>171</v>
       </c>
       <c r="L19" s="3" t="s">
@@ -7353,13 +7844,13 @@
       </c>
     </row>
     <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G20" s="22" t="s">
+      <c r="G20" s="21" t="s">
         <v>155</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K20" s="22" t="s">
+      <c r="K20" s="21" t="s">
         <v>120</v>
       </c>
       <c r="L20" s="3" t="s">
@@ -7367,13 +7858,13 @@
       </c>
     </row>
     <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G21" s="22" t="s">
+      <c r="G21" s="21" t="s">
         <v>110</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K21" s="22" t="s">
+      <c r="K21" s="21" t="s">
         <v>122</v>
       </c>
       <c r="L21" s="3" t="s">
@@ -7381,140 +7872,144 @@
       </c>
     </row>
     <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G22" s="37" t="s">
+      <c r="G22" s="36" t="s">
         <v>164</v>
       </c>
-      <c r="H22" s="14" t="s">
+      <c r="H22" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="K22" s="23" t="s">
+      <c r="K22" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="L22" s="14" t="s">
+      <c r="L22" s="13" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="K23" s="15"/>
-      <c r="L23" s="15"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="K23" s="14"/>
+      <c r="L23" s="14"/>
     </row>
     <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G24" s="24"/>
-      <c r="H24" s="24"/>
-      <c r="K24" s="24"/>
-      <c r="L24" s="24"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="23"/>
+      <c r="K24" s="23"/>
+      <c r="L24" s="23"/>
     </row>
     <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G25" s="24"/>
-      <c r="H25" s="24"/>
-      <c r="K25" s="24"/>
-      <c r="L25" s="24"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="23"/>
+      <c r="K25" s="23"/>
+      <c r="L25" s="23"/>
     </row>
     <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G26" s="24"/>
-      <c r="H26" s="24"/>
-      <c r="K26" s="24"/>
-      <c r="L26" s="24"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="23"/>
+      <c r="K26" s="23"/>
+      <c r="L26" s="23"/>
     </row>
     <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G27" s="24"/>
-      <c r="H27" s="24"/>
-      <c r="K27" s="24"/>
-      <c r="L27" s="24"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
+      <c r="K27" s="23"/>
+      <c r="L27" s="23"/>
     </row>
     <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G28" s="24"/>
-      <c r="H28" s="24"/>
-      <c r="K28" s="24"/>
-      <c r="L28" s="24"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
     </row>
     <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G29" s="24"/>
-      <c r="H29" s="24"/>
-      <c r="K29" s="24"/>
-      <c r="L29" s="24"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="23"/>
+      <c r="K29" s="23"/>
+      <c r="L29" s="23"/>
     </row>
     <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G30" s="24"/>
-      <c r="H30" s="24"/>
-      <c r="K30" s="24"/>
-      <c r="L30" s="24"/>
+      <c r="G30" s="23"/>
+      <c r="H30" s="23"/>
+      <c r="K30" s="23"/>
+      <c r="L30" s="23"/>
     </row>
     <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G31" s="24"/>
-      <c r="H31" s="24"/>
-      <c r="K31" s="24"/>
-      <c r="L31" s="24"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23"/>
+      <c r="K31" s="23"/>
+      <c r="L31" s="23"/>
     </row>
     <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G32" s="24"/>
-      <c r="H32" s="24"/>
-      <c r="K32" s="24"/>
-      <c r="L32" s="24"/>
+      <c r="G32" s="23"/>
+      <c r="H32" s="23"/>
+      <c r="K32" s="23"/>
+      <c r="L32" s="23"/>
     </row>
     <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G33" s="16"/>
-      <c r="H33" s="16"/>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+      <c r="K33" s="15"/>
+      <c r="L33" s="15"/>
     </row>
     <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G34" s="16"/>
-      <c r="H34" s="16"/>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="15"/>
+      <c r="K34" s="15"/>
+      <c r="L34" s="15"/>
     </row>
     <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G35" s="16"/>
-      <c r="H35" s="16"/>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="15"/>
+      <c r="K35" s="15"/>
+      <c r="L35" s="15"/>
     </row>
     <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G36" s="16"/>
-      <c r="H36" s="16"/>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="15"/>
+      <c r="K36" s="15"/>
+      <c r="L36" s="15"/>
     </row>
     <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G37" s="16"/>
-      <c r="H37" s="16"/>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="15"/>
+      <c r="K37" s="15"/>
+      <c r="L37" s="15"/>
     </row>
     <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G38" s="16"/>
-      <c r="H38" s="16"/>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="15"/>
+      <c r="K38" s="15"/>
+      <c r="L38" s="15"/>
     </row>
     <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G39" s="16"/>
-      <c r="H39" s="16"/>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="15"/>
+      <c r="K39" s="15"/>
+      <c r="L39" s="15"/>
     </row>
     <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G40" s="16"/>
-      <c r="H40" s="16"/>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
+      <c r="G40" s="15"/>
+      <c r="H40" s="15"/>
+      <c r="K40" s="15"/>
+      <c r="L40" s="15"/>
     </row>
     <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G41" s="16"/>
-      <c r="H41" s="16"/>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
+      <c r="G41" s="15"/>
+      <c r="H41" s="15"/>
+      <c r="K41" s="15"/>
+      <c r="L41" s="15"/>
     </row>
     <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G42" s="16"/>
-      <c r="H42" s="16"/>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
+      <c r="G42" s="15"/>
+      <c r="H42" s="15"/>
+      <c r="K42" s="15"/>
+      <c r="L42" s="15"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>